--- a/Docs/数据表demo.xlsx
+++ b/Docs/数据表demo.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15513\Desktop\千秋策（Millennia Stratagem）\Docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480" activeTab="4"/>
+    <workbookView windowWidth="24750" windowHeight="10480" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="卡池总览" sheetId="1" r:id="rId1"/>
@@ -32,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="555">
   <si>
     <t>千秋策 · 朝代卡池总览</t>
   </si>
@@ -458,6 +463,30 @@
   </si>
   <si>
     <t>弃置敌方一张手牌</t>
+  </si>
+  <si>
+    <t>过费类</t>
+  </si>
+  <si>
+    <t>费用上限+1</t>
+  </si>
+  <si>
+    <t>费用上限+2</t>
+  </si>
+  <si>
+    <t>固定5费策略卡</t>
+  </si>
+  <si>
+    <t>回费类</t>
+  </si>
+  <si>
+    <t>回复x点费用</t>
+  </si>
+  <si>
+    <t>x-2</t>
+  </si>
+  <si>
+    <t>x-2费策略卡，2=&lt;x&lt;=5</t>
   </si>
   <si>
     <t>直伤类</t>
@@ -2543,7 +2572,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2630,6 +2659,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3094,7 +3132,7 @@
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="40" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -3113,7 +3151,7 @@
       <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="40" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -3353,7 +3391,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B6:Q64"/>
+  <dimension ref="B6:Q72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="16" customWidth="1"/>
@@ -4056,90 +4094,161 @@
       </c>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="36"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="36"/>
+      <c r="B57" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" s="25">
+        <v>3</v>
+      </c>
+      <c r="E57" s="36" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="36"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="36"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D58" s="25">
+        <v>5</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="36"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="36"/>
+      <c r="B59" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="D60" s="25">
-        <v>2</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>122</v>
-      </c>
+      <c r="B60" s="39"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="39"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="34"/>
-      <c r="C61" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="D61" s="25">
-        <v>1</v>
-      </c>
-      <c r="E61" s="34"/>
+      <c r="B61" s="39"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="39"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="34"/>
+      <c r="B62" s="39"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
-      <c r="E62" s="34"/>
+      <c r="E62" s="39"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="34"/>
-      <c r="C63" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="D63" s="25">
+      <c r="B63" s="39"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="39"/>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="B64" s="39"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="39"/>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" s="39"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="39"/>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="B66" s="39"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="39"/>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" s="39"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="39"/>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="25">
+        <v>2</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="B69" s="34"/>
+      <c r="C69" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" s="25">
+        <v>1</v>
+      </c>
+      <c r="E69" s="34"/>
+    </row>
+    <row r="70" spans="2:5">
+      <c r="B70" s="34"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="34"/>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="B71" s="34"/>
+      <c r="C71" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="D71" s="25">
         <v>6</v>
       </c>
-      <c r="E63" s="35"/>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="B64" s="35"/>
-      <c r="C64" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="D64" s="25">
+      <c r="E71" s="35"/>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="B72" s="35"/>
+      <c r="C72" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" s="25">
         <v>3</v>
       </c>
-      <c r="E64" s="25" t="s">
-        <v>147</v>
+      <c r="E72" s="25" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="B37:B41"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B68:B72"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="E37:E40"/>
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E45:E47"/>
     <mergeCell ref="E50:E52"/>
-    <mergeCell ref="E60:E63"/>
+    <mergeCell ref="E68:E71"/>
     <mergeCell ref="B23:E24"/>
     <mergeCell ref="B17:E18"/>
     <mergeCell ref="B20:E21"/>
@@ -4163,7 +4272,7 @@
   <sheetData>
     <row r="3" spans="2:14">
       <c r="E3" s="16" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="2:14">
@@ -4198,7 +4307,7 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C7" s="18">
         <v>1</v>
@@ -4636,17 +4745,17 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:23">
       <c r="A1" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -4673,18 +4782,18 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="7" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B6" s="11">
         <f>基础公式!E9</f>
@@ -4697,7 +4806,7 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B7" s="11">
         <f>基础公式!E10</f>
@@ -4710,7 +4819,7 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B8" s="11">
         <f>基础公式!E11</f>
@@ -4723,7 +4832,7 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B9" s="11">
         <f>基础公式!E12</f>
@@ -4736,7 +4845,7 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -4763,13 +4872,13 @@
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" ht="108" spans="1:23">
@@ -4780,7 +4889,7 @@
         <v>0.5</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:23">
@@ -4791,7 +4900,7 @@
         <v>0.5</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" ht="96" spans="1:23">
@@ -4802,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" ht="60" spans="1:23">
@@ -4813,7 +4922,7 @@
         <v>1.5</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" ht="48" spans="1:3">
@@ -4824,117 +4933,117 @@
         <v>1</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" ht="24" spans="1:3">
       <c r="A18" s="8" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B18" s="12">
         <v>1</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" ht="24" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B19" s="12">
         <v>3</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" ht="24" spans="1:3">
       <c r="A20" s="8" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B20" s="12">
         <v>6</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" ht="36" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B21" s="12">
         <v>0.5</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" ht="36" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B22" s="12">
         <v>1</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" ht="24" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B23" s="12">
         <v>1</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" ht="24" spans="1:3">
       <c r="A24" s="8" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B24" s="12">
         <v>2</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" ht="24" spans="1:3">
       <c r="A25" s="8" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B25" s="12">
         <v>3</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" ht="24" spans="1:3">
       <c r="A26" s="8" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B26" s="12">
         <v>2</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" ht="24" spans="1:3">
       <c r="A27" s="8" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B27" s="12">
         <v>1.5</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" ht="60" spans="1:3">
@@ -4945,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" ht="24" spans="1:3">
@@ -4956,7 +5065,7 @@
         <v>2.5</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" ht="24" spans="1:3">
@@ -4967,7 +5076,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" ht="60" spans="1:3">
@@ -4978,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" ht="24" spans="1:3">
@@ -4989,144 +5098,144 @@
         <v>0.5</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:23">
       <c r="A33" s="8" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B33" s="12">
         <v>3</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" ht="36" spans="1:23">
       <c r="A34" s="8" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B34" s="12">
         <v>2</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" ht="36" spans="1:23">
       <c r="A35" s="8" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B35" s="12">
         <v>2</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" ht="24" spans="1:23">
       <c r="A36" s="8" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B36" s="12">
         <v>2</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" ht="60" spans="1:23">
       <c r="A37" s="8" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B37" s="12">
         <v>2</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" ht="60" spans="1:23">
       <c r="A38" s="8" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B38" s="12">
         <v>1</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:23">
       <c r="A39" s="8" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B39" s="12">
         <v>6</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" ht="60" spans="1:23">
       <c r="A40" s="8" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B40" s="12">
         <v>3</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:23">
       <c r="A42" s="8" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B42" s="12">
         <v>0.75</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" ht="24" spans="1:23">
       <c r="A43" s="8" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B43" s="12">
         <v>0.5</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" ht="36" spans="1:23">
       <c r="A44" s="8" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B44" s="12">
         <v>0.6</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" ht="84" spans="1:23">
       <c r="A45" s="8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -5153,28 +5262,28 @@
     </row>
     <row r="48" ht="30" customHeight="1" spans="1:23">
       <c r="A48" s="7" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>59</v>
@@ -5183,43 +5292,43 @@
         <v>60</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Q48" s="7" t="s">
         <v>80</v>
       </c>
       <c r="R48" s="7" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="T48" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="U48" s="7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="V48" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W48" s="7" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -5227,10 +5336,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>30</v>
@@ -5242,10 +5351,10 @@
         <v>5</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I49" s="8">
         <v>1</v>
@@ -5269,10 +5378,10 @@
       <c r="P49" s="10"/>
       <c r="Q49" s="9"/>
       <c r="R49" s="13" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="S49" s="9" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="T49" s="14">
         <v>0</v>
@@ -5295,10 +5404,10 @@
         <v>2</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>30</v>
@@ -5310,10 +5419,10 @@
         <v>5</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I50" s="8">
         <v>2</v>
@@ -5337,10 +5446,10 @@
       <c r="P50" s="10"/>
       <c r="Q50" s="9"/>
       <c r="R50" s="13" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="S50" s="9" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="T50" s="14">
         <v>0</v>
@@ -5363,10 +5472,10 @@
         <v>3</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>30</v>
@@ -5378,10 +5487,10 @@
         <v>5</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I51" s="8">
         <v>3</v>
@@ -5405,10 +5514,10 @@
       <c r="P51" s="10"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="13" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="S51" s="9" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="T51" s="14">
         <v>0</v>
@@ -5431,10 +5540,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>30</v>
@@ -5446,10 +5555,10 @@
         <v>5</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I52" s="8">
         <v>2</v>
@@ -5473,10 +5582,10 @@
       <c r="P52" s="10"/>
       <c r="Q52" s="9"/>
       <c r="R52" s="13" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="S52" s="9" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="T52" s="14">
         <v>0</v>
@@ -5499,10 +5608,10 @@
         <v>5</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>30</v>
@@ -5514,10 +5623,10 @@
         <v>5</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I53" s="8">
         <v>3</v>
@@ -5540,13 +5649,13 @@
       <c r="O53" s="10"/>
       <c r="P53" s="10"/>
       <c r="Q53" s="9" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="R53" s="13" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="S53" s="9" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="T53" s="14">
         <v>1.5</v>
@@ -5569,10 +5678,10 @@
         <v>6</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>30</v>
@@ -5584,10 +5693,10 @@
         <v>5</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I54" s="8">
         <v>2</v>
@@ -5611,14 +5720,14 @@
         <v>83</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Q54" s="9"/>
       <c r="R54" s="13" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="S54" s="9" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="T54" s="14">
         <v>0</v>
@@ -5641,10 +5750,10 @@
         <v>7</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>30</v>
@@ -5656,10 +5765,10 @@
         <v>6</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I55" s="8">
         <v>1</v>
@@ -5674,13 +5783,13 @@
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="9" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="R55" s="13" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="S55" s="9" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="T55" s="14">
         <v>1</v>
@@ -5703,10 +5812,10 @@
         <v>8</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>30</v>
@@ -5718,10 +5827,10 @@
         <v>6</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I56" s="8">
         <v>2</v>
@@ -5736,13 +5845,13 @@
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
       <c r="Q56" s="9" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="S56" s="9" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="T56" s="14">
         <v>2</v>
@@ -5765,10 +5874,10 @@
         <v>9</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>30</v>
@@ -5780,10 +5889,10 @@
         <v>5</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I57" s="8">
         <v>3</v>
@@ -5804,17 +5913,17 @@
         <v>1</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="13" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="S57" s="9" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="T57" s="14">
         <v>0.5</v>
@@ -5837,10 +5946,10 @@
         <v>10</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>30</v>
@@ -5852,10 +5961,10 @@
         <v>5</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I58" s="8">
         <v>3</v>
@@ -5876,17 +5985,17 @@
         <v>1</v>
       </c>
       <c r="O58" s="10" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="P58" s="10" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="Q58" s="9"/>
       <c r="R58" s="13" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="S58" s="9" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="T58" s="14">
         <v>1</v>
@@ -5909,10 +6018,10 @@
         <v>11</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>30</v>
@@ -5924,10 +6033,10 @@
         <v>5</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I59" s="8">
         <v>3</v>
@@ -5951,10 +6060,10 @@
       <c r="P59" s="10"/>
       <c r="Q59" s="9"/>
       <c r="R59" s="13" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="S59" s="9" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="T59" s="14">
         <v>0</v>
@@ -5977,10 +6086,10 @@
         <v>12</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>30</v>
@@ -5992,10 +6101,10 @@
         <v>5</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I60" s="8">
         <v>4</v>
@@ -6019,14 +6128,14 @@
         <v>113</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="Q60" s="9"/>
       <c r="R60" s="13" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="S60" s="9" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="T60" s="14">
         <v>1</v>
@@ -6049,10 +6158,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>30</v>
@@ -6064,10 +6173,10 @@
         <v>5</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I61" s="8">
         <v>4</v>
@@ -6091,14 +6200,14 @@
         <v>91</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="13" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="S61" s="9" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="T61" s="14">
         <v>1.5</v>
@@ -6121,10 +6230,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>30</v>
@@ -6136,10 +6245,10 @@
         <v>5</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I62" s="8">
         <v>4</v>
@@ -6163,14 +6272,14 @@
         <v>83</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Q62" s="9"/>
       <c r="R62" s="13" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="S62" s="9" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="T62" s="14">
         <v>0</v>
@@ -6193,10 +6302,10 @@
         <v>15</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>30</v>
@@ -6208,10 +6317,10 @@
         <v>6</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I63" s="8">
         <v>4</v>
@@ -6226,13 +6335,13 @@
       <c r="O63" s="10"/>
       <c r="P63" s="10"/>
       <c r="Q63" s="9" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="R63" s="13" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="S63" s="9" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="T63" s="14">
         <v>4</v>
@@ -6255,10 +6364,10 @@
         <v>16</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>30</v>
@@ -6270,10 +6379,10 @@
         <v>6</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I64" s="8">
         <v>2</v>
@@ -6288,13 +6397,13 @@
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
       <c r="Q64" s="9" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="R64" s="13" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="S64" s="9" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="T64" s="14">
         <v>2</v>
@@ -6317,25 +6426,25 @@
         <v>17</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I65" s="8">
         <v>3</v>
@@ -6359,14 +6468,14 @@
         <v>93</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="13" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="S65" s="9" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="T65" s="14">
         <v>1</v>
@@ -6389,25 +6498,25 @@
         <v>18</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I66" s="8">
         <v>2</v>
@@ -6422,13 +6531,13 @@
       <c r="O66" s="10"/>
       <c r="P66" s="10"/>
       <c r="Q66" s="9" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="R66" s="13" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="S66" s="9" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="T66" s="14">
         <v>2</v>
@@ -6451,25 +6560,25 @@
         <v>19</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I67" s="8">
         <v>5</v>
@@ -6490,17 +6599,17 @@
         <v>1</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="13" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="S67" s="9" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="T67" s="14">
         <v>2</v>
@@ -6523,25 +6632,25 @@
         <v>20</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I68" s="8">
         <v>4</v>
@@ -6556,13 +6665,13 @@
       <c r="O68" s="10"/>
       <c r="P68" s="10"/>
       <c r="Q68" s="9" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="R68" s="13" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="S68" s="9" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="T68" s="14">
         <v>4</v>
@@ -6585,25 +6694,25 @@
         <v>21</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I69" s="8">
         <v>6</v>
@@ -6621,10 +6730,10 @@
         <v>100</v>
       </c>
       <c r="R69" s="13" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="S69" s="9" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="T69" s="14">
         <v>6</v>
@@ -6647,25 +6756,25 @@
         <v>22</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I70" s="8">
         <v>6</v>
@@ -6686,17 +6795,17 @@
         <v>1</v>
       </c>
       <c r="O70" s="10" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q70" s="9"/>
       <c r="R70" s="13" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="S70" s="9" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="T70" s="14">
         <v>1.5</v>
@@ -6719,25 +6828,25 @@
         <v>23</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I71" s="8">
         <v>6</v>
@@ -6758,17 +6867,17 @@
         <v>1</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="13" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="S71" s="9" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="T71" s="14">
         <v>2</v>
@@ -6791,25 +6900,25 @@
         <v>24</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I72" s="8">
         <v>6</v>
@@ -6833,10 +6942,10 @@
       <c r="P72" s="10"/>
       <c r="Q72" s="9"/>
       <c r="R72" s="13" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="S72" s="9" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="T72" s="14">
         <v>0</v>
@@ -6856,42 +6965,42 @@
     </row>
     <row r="74" customHeight="1" spans="1:23">
       <c r="A74" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:23">
       <c r="A75" s="3" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:23">
       <c r="A76" s="3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:23">
       <c r="A77" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:23">
       <c r="A78" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:23">
       <c r="A79" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:23">
       <c r="A80" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:1">
       <c r="A81" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -6970,17 +7079,17 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:23">
       <c r="A1" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -7007,18 +7116,18 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="7" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B6" s="11">
         <f>基础公式!E9</f>
@@ -7031,7 +7140,7 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B7" s="11">
         <f>基础公式!E10</f>
@@ -7044,7 +7153,7 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B8" s="11">
         <f>基础公式!E11</f>
@@ -7057,7 +7166,7 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B9" s="11">
         <f>基础公式!E12</f>
@@ -7070,7 +7179,7 @@
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -7097,13 +7206,13 @@
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" ht="108" spans="1:23">
@@ -7114,7 +7223,7 @@
         <v>0.5</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:23">
@@ -7125,7 +7234,7 @@
         <v>0.5</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" ht="96" spans="1:23">
@@ -7136,7 +7245,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" ht="60" spans="1:23">
@@ -7147,7 +7256,7 @@
         <v>1.5</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" ht="48" spans="1:3">
@@ -7158,117 +7267,117 @@
         <v>1</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" ht="24" spans="1:3">
       <c r="A18" s="8" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B18" s="12">
         <v>1</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" ht="24" spans="1:3">
       <c r="A19" s="8" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B19" s="12">
         <v>3</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" ht="24" spans="1:3">
       <c r="A20" s="8" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B20" s="12">
         <v>6</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" ht="36" spans="1:3">
       <c r="A21" s="8" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B21" s="12">
         <v>0.5</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" ht="36" spans="1:3">
       <c r="A22" s="8" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B22" s="12">
         <v>1</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" ht="24" spans="1:3">
       <c r="A23" s="8" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B23" s="12">
         <v>1</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" ht="24" spans="1:3">
       <c r="A24" s="8" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B24" s="12">
         <v>2</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" ht="24" spans="1:3">
       <c r="A25" s="8" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B25" s="12">
         <v>3</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" ht="24" spans="1:3">
       <c r="A26" s="8" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B26" s="12">
         <v>2</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" ht="24" spans="1:3">
       <c r="A27" s="8" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B27" s="12">
         <v>1.5</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" ht="60" spans="1:3">
@@ -7279,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" ht="24" spans="1:3">
@@ -7290,7 +7399,7 @@
         <v>2.5</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" ht="24" spans="1:3">
@@ -7301,7 +7410,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" ht="60" spans="1:3">
@@ -7312,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="32" ht="24" spans="1:3">
@@ -7323,144 +7432,144 @@
         <v>0.5</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" ht="36" spans="1:23">
       <c r="A33" s="8" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B33" s="12">
         <v>3</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" ht="36" spans="1:23">
       <c r="A34" s="8" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B34" s="12">
         <v>2</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35" ht="36" spans="1:23">
       <c r="A35" s="8" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B35" s="12">
         <v>2</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36" ht="24" spans="1:23">
       <c r="A36" s="8" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B36" s="12">
         <v>2</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" ht="60" spans="1:23">
       <c r="A37" s="8" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B37" s="12">
         <v>2</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" ht="60" spans="1:23">
       <c r="A38" s="8" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B38" s="12">
         <v>1</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" ht="60" spans="1:23">
       <c r="A39" s="8" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B39" s="12">
         <v>6</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" ht="60" spans="1:23">
       <c r="A40" s="8" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B40" s="12">
         <v>3</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" ht="84" spans="1:23">
       <c r="A42" s="8" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B42" s="12">
         <v>0.75</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" ht="24" spans="1:23">
       <c r="A43" s="8" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B43" s="12">
         <v>0.5</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" ht="36" spans="1:23">
       <c r="A44" s="8" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B44" s="12">
         <v>0.6</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" ht="84" spans="1:23">
       <c r="A45" s="8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:23">
       <c r="A47" s="4" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -7487,28 +7596,28 @@
     </row>
     <row r="48" ht="30" customHeight="1" spans="1:23">
       <c r="A48" s="7" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>59</v>
@@ -7517,43 +7626,43 @@
         <v>60</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Q48" s="7" t="s">
         <v>80</v>
       </c>
       <c r="R48" s="7" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="T48" s="7" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="U48" s="7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="V48" s="7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="W48" s="7" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -7561,10 +7670,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>31</v>
@@ -7576,10 +7685,10 @@
         <v>5</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I49" s="8">
         <v>2</v>
@@ -7603,10 +7712,10 @@
       <c r="P49" s="10"/>
       <c r="Q49" s="9"/>
       <c r="R49" s="13" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="S49" s="9" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="T49" s="14">
         <v>0</v>
@@ -7629,10 +7738,10 @@
         <v>2</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>31</v>
@@ -7644,10 +7753,10 @@
         <v>5</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I50" s="8">
         <v>1</v>
@@ -7671,14 +7780,14 @@
         <v>83</v>
       </c>
       <c r="P50" s="10" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Q50" s="9"/>
       <c r="R50" s="13" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="S50" s="9" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="T50" s="14">
         <v>0</v>
@@ -7701,10 +7810,10 @@
         <v>3</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>31</v>
@@ -7716,10 +7825,10 @@
         <v>5</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I51" s="8">
         <v>2</v>
@@ -7743,10 +7852,10 @@
       <c r="P51" s="10"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="13" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="S51" s="9" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="T51" s="14">
         <v>0</v>
@@ -7769,10 +7878,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>31</v>
@@ -7784,10 +7893,10 @@
         <v>5</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I52" s="8">
         <v>3</v>
@@ -7811,10 +7920,10 @@
       <c r="P52" s="10"/>
       <c r="Q52" s="9"/>
       <c r="R52" s="13" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="S52" s="9" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="T52" s="14">
         <v>0</v>
@@ -7837,10 +7946,10 @@
         <v>5</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>31</v>
@@ -7852,10 +7961,10 @@
         <v>5</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I53" s="8">
         <v>3</v>
@@ -7878,13 +7987,13 @@
       <c r="O53" s="10"/>
       <c r="P53" s="10"/>
       <c r="Q53" s="9" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="R53" s="13" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="S53" s="9" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="T53" s="14">
         <v>1.5</v>
@@ -7907,10 +8016,10 @@
         <v>6</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>31</v>
@@ -7922,10 +8031,10 @@
         <v>5</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I54" s="8">
         <v>3</v>
@@ -7946,17 +8055,17 @@
         <v>1</v>
       </c>
       <c r="O54" s="10" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="P54" s="10" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="Q54" s="9"/>
       <c r="R54" s="13" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="S54" s="9" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="T54" s="14">
         <v>1</v>
@@ -7979,10 +8088,10 @@
         <v>7</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>31</v>
@@ -7994,10 +8103,10 @@
         <v>6</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I55" s="8">
         <v>1</v>
@@ -8012,13 +8121,13 @@
       <c r="O55" s="10"/>
       <c r="P55" s="10"/>
       <c r="Q55" s="9" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="R55" s="13" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="S55" s="9" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="T55" s="14">
         <v>1</v>
@@ -8041,10 +8150,10 @@
         <v>8</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>31</v>
@@ -8056,10 +8165,10 @@
         <v>6</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I56" s="8">
         <v>3</v>
@@ -8074,13 +8183,13 @@
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
       <c r="Q56" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="S56" s="9" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="T56" s="14">
         <v>3</v>
@@ -8103,10 +8212,10 @@
         <v>9</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>31</v>
@@ -8118,10 +8227,10 @@
         <v>5</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I57" s="8">
         <v>3</v>
@@ -8142,17 +8251,17 @@
         <v>1</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="13" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="S57" s="9" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="T57" s="14">
         <v>0.5</v>
@@ -8175,10 +8284,10 @@
         <v>10</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>31</v>
@@ -8190,10 +8299,10 @@
         <v>5</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I58" s="8">
         <v>3</v>
@@ -8217,10 +8326,10 @@
       <c r="P58" s="10"/>
       <c r="Q58" s="9"/>
       <c r="R58" s="13" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="S58" s="9" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="T58" s="14">
         <v>0</v>
@@ -8243,10 +8352,10 @@
         <v>11</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>31</v>
@@ -8258,10 +8367,10 @@
         <v>5</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I59" s="8">
         <v>3</v>
@@ -8285,14 +8394,14 @@
         <v>88</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="13" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="S59" s="9" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="T59" s="14">
         <v>1</v>
@@ -8315,10 +8424,10 @@
         <v>12</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>31</v>
@@ -8330,10 +8439,10 @@
         <v>5</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I60" s="8">
         <v>4</v>
@@ -8357,14 +8466,14 @@
         <v>113</v>
       </c>
       <c r="P60" s="10" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="Q60" s="9"/>
       <c r="R60" s="13" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="S60" s="9" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="T60" s="14">
         <v>1</v>
@@ -8387,10 +8496,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>31</v>
@@ -8402,10 +8511,10 @@
         <v>5</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="I61" s="8">
         <v>4</v>
@@ -8429,14 +8538,14 @@
         <v>91</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="13" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="S61" s="9" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="T61" s="14">
         <v>1.5</v>
@@ -8459,10 +8568,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>31</v>
@@ -8474,10 +8583,10 @@
         <v>5</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I62" s="8">
         <v>4</v>
@@ -8501,14 +8610,14 @@
         <v>83</v>
       </c>
       <c r="P62" s="10" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="Q62" s="9"/>
       <c r="R62" s="13" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="S62" s="9" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="T62" s="14">
         <v>0</v>
@@ -8531,10 +8640,10 @@
         <v>15</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>31</v>
@@ -8546,10 +8655,10 @@
         <v>6</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I63" s="8">
         <v>4</v>
@@ -8564,13 +8673,13 @@
       <c r="O63" s="10"/>
       <c r="P63" s="10"/>
       <c r="Q63" s="9" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="R63" s="13" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="S63" s="9" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="T63" s="14">
         <v>4</v>
@@ -8593,10 +8702,10 @@
         <v>16</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>31</v>
@@ -8608,10 +8717,10 @@
         <v>6</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I64" s="8">
         <v>2</v>
@@ -8626,13 +8735,13 @@
       <c r="O64" s="10"/>
       <c r="P64" s="10"/>
       <c r="Q64" s="9" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="R64" s="13" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="S64" s="9" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="T64" s="14">
         <v>2</v>
@@ -8655,25 +8764,25 @@
         <v>17</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I65" s="8">
         <v>3</v>
@@ -8697,14 +8806,14 @@
         <v>93</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="13" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="S65" s="9" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="T65" s="14">
         <v>1</v>
@@ -8727,25 +8836,25 @@
         <v>18</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I66" s="8">
         <v>4</v>
@@ -8760,13 +8869,13 @@
       <c r="O66" s="10"/>
       <c r="P66" s="10"/>
       <c r="Q66" s="9" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="R66" s="13" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="S66" s="9" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="T66" s="14">
         <v>4</v>
@@ -8789,25 +8898,25 @@
         <v>19</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I67" s="8">
         <v>5</v>
@@ -8828,17 +8937,17 @@
         <v>1</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="13" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="S67" s="9" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="T67" s="14">
         <v>3.5</v>
@@ -8861,25 +8970,25 @@
         <v>20</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I68" s="8">
         <v>5</v>
@@ -8900,17 +9009,17 @@
         <v>1</v>
       </c>
       <c r="O68" s="10" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="P68" s="10" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="Q68" s="9"/>
       <c r="R68" s="13" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="S68" s="9" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="T68" s="14">
         <v>0.5</v>
@@ -8933,25 +9042,25 @@
         <v>21</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="I69" s="8">
         <v>5</v>
@@ -8966,13 +9075,13 @@
       <c r="O69" s="10"/>
       <c r="P69" s="10"/>
       <c r="Q69" s="9" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="R69" s="13" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="S69" s="9" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="T69" s="14">
         <v>5</v>
@@ -8995,25 +9104,25 @@
         <v>22</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I70" s="8">
         <v>6</v>
@@ -9034,17 +9143,17 @@
         <v>1</v>
       </c>
       <c r="O70" s="10" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Q70" s="9"/>
       <c r="R70" s="13" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="S70" s="9" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="T70" s="14">
         <v>1.5</v>
@@ -9067,25 +9176,25 @@
         <v>23</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I71" s="8">
         <v>6</v>
@@ -9106,17 +9215,17 @@
         <v>1</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="13" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="S71" s="9" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="T71" s="14">
         <v>3.5</v>
@@ -9139,25 +9248,25 @@
         <v>24</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>31</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I72" s="8">
         <v>6</v>
@@ -9178,15 +9287,15 @@
         <v>2</v>
       </c>
       <c r="O72" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="P72" s="10"/>
       <c r="Q72" s="9"/>
       <c r="R72" s="13" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="S72" s="9" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="T72" s="14">
         <v>0.5</v>
@@ -9206,42 +9315,42 @@
     </row>
     <row r="74" customHeight="1" spans="1:23">
       <c r="A74" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:23">
       <c r="A75" s="3" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:23">
       <c r="A76" s="3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:23">
       <c r="A77" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:23">
       <c r="A78" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:23">
       <c r="A79" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:23">
       <c r="A80" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:1">
       <c r="A81" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -9309,17 +9418,17 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -9328,19 +9437,19 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1" spans="1:5">
@@ -9348,16 +9457,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1" spans="1:5">
@@ -9365,16 +9474,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1" spans="1:5">
@@ -9382,16 +9491,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1" spans="1:5">
@@ -9399,16 +9508,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1" spans="1:5">
@@ -9416,16 +9525,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1" spans="1:5">
@@ -9433,16 +9542,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1" spans="1:5">
@@ -9453,13 +9562,13 @@
         <v>117</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1" spans="1:5">
@@ -9470,18 +9579,18 @@
         <v>118</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -9490,19 +9599,19 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="7" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5">
@@ -9510,16 +9619,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5">
@@ -9527,16 +9636,16 @@
         <v>2</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5">
@@ -9544,16 +9653,16 @@
         <v>3</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5">
@@ -9561,16 +9670,16 @@
         <v>4</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5">
@@ -9581,13 +9690,13 @@
         <v>117</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5">
@@ -9598,13 +9707,13 @@
         <v>123</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:5">
@@ -9612,16 +9721,16 @@
         <v>7</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5">
@@ -9629,16 +9738,16 @@
         <v>8</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5">
@@ -9646,16 +9755,16 @@
         <v>9</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:5">
@@ -9663,16 +9772,16 @@
         <v>10</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -9680,16 +9789,16 @@
         <v>11</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -9697,16 +9806,16 @@
         <v>12</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5">
@@ -9714,21 +9823,21 @@
         <v>13</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -9737,52 +9846,52 @@
     </row>
     <row r="32" customHeight="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:1">
       <c r="A33" s="3" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:1">
       <c r="A34" s="3" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:1">
       <c r="A35" s="3" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:1">
       <c r="A36" s="3" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:1">
       <c r="A37" s="3" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:1">
       <c r="A38" s="3" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:1">
       <c r="A39" s="3" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:1">
       <c r="A40" s="3" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:1">
       <c r="A41" s="3" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
